--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_20.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:M148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,1415 +469,6645 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:15.680</t>
+          <t>2026-05-29 09:43:46.148</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779504971273</v>
+        <v>1780022624927</v>
       </c>
       <c r="C2" t="n">
-        <v>94741</v>
+        <v>81377</v>
       </c>
       <c r="D2" t="n">
-        <v>3064.15</v>
+        <v>-995.3200000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F2" t="n">
-        <v>483</v>
+        <v>1419</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>316.88</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1221</v>
+      </c>
+      <c r="L2" t="n">
+        <v>113</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.675</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:15.684</t>
+          <t>2026-05-29 09:43:46.411</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779504971474</v>
+        <v>1780022625127</v>
       </c>
       <c r="C3" t="n">
-        <v>94889</v>
+        <v>81248</v>
       </c>
       <c r="D3" t="n">
-        <v>3058.95</v>
+        <v>-1074.56</v>
       </c>
       <c r="E3" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F3" t="n">
-        <v>483</v>
+        <v>1419</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>316.88</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1282</v>
+      </c>
+      <c r="L3" t="n">
+        <v>117</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.123</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:16.006</t>
+          <t>2026-05-29 09:43:46.421</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779504971676</v>
+        <v>1780022625346</v>
       </c>
       <c r="C4" t="n">
-        <v>94509</v>
+        <v>81369</v>
       </c>
       <c r="D4" t="n">
-        <v>2526</v>
+        <v>-899.83</v>
       </c>
       <c r="E4" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F4" t="n">
-        <v>483</v>
+        <v>1419</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>316.88</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1074</v>
+      </c>
+      <c r="L4" t="n">
+        <v>113</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.043</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:16.009</t>
+          <t>2026-05-29 09:43:46.747</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779504971877</v>
+        <v>1780022625546</v>
       </c>
       <c r="C5" t="n">
-        <v>94588</v>
+        <v>81377</v>
       </c>
       <c r="D5" t="n">
-        <v>2478.7</v>
+        <v>-846.84</v>
       </c>
       <c r="E5" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F5" t="n">
-        <v>483</v>
+        <v>5776</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>316.88</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1199</v>
+      </c>
+      <c r="L5" t="n">
+        <v>119</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.533</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:16.596</t>
+          <t>2026-05-29 09:43:46.769</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779504972078</v>
+        <v>1780022625746</v>
       </c>
       <c r="C6" t="n">
-        <v>94660</v>
+        <v>81904</v>
       </c>
       <c r="D6" t="n">
-        <v>2426.76</v>
+        <v>-277.49</v>
       </c>
       <c r="E6" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F6" t="n">
-        <v>483</v>
+        <v>5776</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>316.88</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1021</v>
+      </c>
+      <c r="L6" t="n">
+        <v>110</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:16.922</t>
+          <t>2026-05-29 09:43:46.771</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779504972279</v>
+        <v>1780022625946</v>
       </c>
       <c r="C7" t="n">
-        <v>94670</v>
+        <v>82088</v>
       </c>
       <c r="D7" t="n">
-        <v>2315.43</v>
+        <v>-79.62</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F7" t="n">
-        <v>1006</v>
+        <v>5776</v>
       </c>
       <c r="G7" t="n">
-        <v>369.82</v>
+        <v>316.88</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K7" t="n">
+        <v>823</v>
+      </c>
+      <c r="L7" t="n">
+        <v>110</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.521</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:17.329</t>
+          <t>2026-05-29 09:43:47.273</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779504972480</v>
+        <v>1780022626146</v>
       </c>
       <c r="C8" t="n">
-        <v>94388</v>
+        <v>81932</v>
       </c>
       <c r="D8" t="n">
-        <v>1917.65</v>
+        <v>-231.64</v>
       </c>
       <c r="E8" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F8" t="n">
-        <v>1006</v>
+        <v>5776</v>
       </c>
       <c r="G8" t="n">
-        <v>369.82</v>
+        <v>316.88</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1126</v>
+      </c>
+      <c r="L8" t="n">
+        <v>126</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.379</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:17.331</t>
+          <t>2026-05-29 09:43:47.332</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779504972681</v>
+        <v>1780022626346</v>
       </c>
       <c r="C9" t="n">
-        <v>94474</v>
+        <v>82039</v>
       </c>
       <c r="D9" t="n">
-        <v>1907.77</v>
+        <v>-113.06</v>
       </c>
       <c r="E9" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F9" t="n">
-        <v>1006</v>
+        <v>5776</v>
       </c>
       <c r="G9" t="n">
-        <v>369.82</v>
+        <v>316.88</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K9" t="n">
+        <v>985</v>
+      </c>
+      <c r="L9" t="n">
+        <v>108</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.991</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:17.375</t>
+          <t>2026-05-29 09:43:48.036</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779504972883</v>
+        <v>1780022626546</v>
       </c>
       <c r="C10" t="n">
-        <v>94568</v>
+        <v>81776</v>
       </c>
       <c r="D10" t="n">
-        <v>1906.38</v>
+        <v>-370.4</v>
       </c>
       <c r="E10" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F10" t="n">
-        <v>1006</v>
+        <v>5776</v>
       </c>
       <c r="G10" t="n">
-        <v>369.82</v>
+        <v>316.88</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1488</v>
+      </c>
+      <c r="L10" t="n">
+        <v>121</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.309</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:17.960</t>
+          <t>2026-05-29 09:43:48.038</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779504973084</v>
+        <v>1780022626746</v>
       </c>
       <c r="C11" t="n">
-        <v>94617</v>
+        <v>81622</v>
       </c>
       <c r="D11" t="n">
-        <v>1860.06</v>
+        <v>-505.88</v>
       </c>
       <c r="E11" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F11" t="n">
-        <v>724</v>
+        <v>5776</v>
       </c>
       <c r="G11" t="n">
-        <v>261.77</v>
+        <v>316.88</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1290</v>
+      </c>
+      <c r="L11" t="n">
+        <v>108</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.611</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:17.962</t>
+          <t>2026-05-29 09:43:48.040</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779504973285</v>
+        <v>1780022626965</v>
       </c>
       <c r="C12" t="n">
-        <v>94515</v>
+        <v>81897</v>
       </c>
       <c r="D12" t="n">
-        <v>1665.06</v>
+        <v>-205.59</v>
       </c>
       <c r="E12" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F12" t="n">
-        <v>724</v>
+        <v>5776</v>
       </c>
       <c r="G12" t="n">
-        <v>261.77</v>
+        <v>316.88</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1073</v>
+      </c>
+      <c r="L12" t="n">
+        <v>112</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.217</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:18.375</t>
+          <t>2026-05-29 09:43:48.368</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779504973486</v>
+        <v>1780022627165</v>
       </c>
       <c r="C13" t="n">
-        <v>94611</v>
+        <v>83132</v>
       </c>
       <c r="D13" t="n">
-        <v>1677.81</v>
+        <v>1039.69</v>
       </c>
       <c r="E13" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F13" t="n">
-        <v>724</v>
+        <v>1619</v>
       </c>
       <c r="G13" t="n">
-        <v>261.77</v>
+        <v>316.88</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="L13" t="n">
+        <v>119</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.711</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:18.377</t>
+          <t>2026-05-29 09:43:48.369</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779504973687</v>
+        <v>1780022627365</v>
       </c>
       <c r="C14" t="n">
-        <v>94753</v>
+        <v>84400</v>
       </c>
       <c r="D14" t="n">
-        <v>1735.92</v>
+        <v>2255.71</v>
       </c>
       <c r="E14" t="n">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="F14" t="n">
-        <v>584</v>
+        <v>1619</v>
       </c>
       <c r="G14" t="n">
-        <v>227.12</v>
+        <v>316.88</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1003</v>
+      </c>
+      <c r="L14" t="n">
+        <v>109</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.956</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:18.797</t>
+          <t>2026-05-29 09:43:48.370</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779504973888</v>
+        <v>1780022627565</v>
       </c>
       <c r="C15" t="n">
-        <v>94670</v>
+        <v>83471</v>
       </c>
       <c r="D15" t="n">
-        <v>1566.12</v>
+        <v>1213.92</v>
       </c>
       <c r="E15" t="n">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="F15" t="n">
-        <v>584</v>
+        <v>1619</v>
       </c>
       <c r="G15" t="n">
-        <v>227.12</v>
+        <v>316.88</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K15" t="n">
+        <v>804</v>
+      </c>
+      <c r="L15" t="n">
+        <v>115</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.379</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:18.799</t>
+          <t>2026-05-29 09:43:48.774</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779504974090</v>
+        <v>1780022627765</v>
       </c>
       <c r="C16" t="n">
-        <v>94725</v>
+        <v>83077</v>
       </c>
       <c r="D16" t="n">
-        <v>1542.82</v>
+        <v>759.22</v>
       </c>
       <c r="E16" t="n">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="F16" t="n">
-        <v>584</v>
+        <v>1619</v>
       </c>
       <c r="G16" t="n">
-        <v>227.12</v>
+        <v>316.88</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1007</v>
+      </c>
+      <c r="L16" t="n">
+        <v>115</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.207</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:18.801</t>
+          <t>2026-05-29 09:43:48.869</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779504974291</v>
+        <v>1780022627965</v>
       </c>
       <c r="C17" t="n">
-        <v>94760</v>
+        <v>82496</v>
       </c>
       <c r="D17" t="n">
-        <v>1500.67</v>
+        <v>140.26</v>
       </c>
       <c r="E17" t="n">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="F17" t="n">
-        <v>584</v>
+        <v>1619</v>
       </c>
       <c r="G17" t="n">
-        <v>227.12</v>
+        <v>316.88</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K17" t="n">
+        <v>903</v>
+      </c>
+      <c r="L17" t="n">
+        <v>109</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.948</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:19.082</t>
+          <t>2026-05-29 09:43:49.388</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779504974492</v>
+        <v>1780022628165</v>
       </c>
       <c r="C18" t="n">
-        <v>94823</v>
+        <v>82380</v>
       </c>
       <c r="D18" t="n">
-        <v>1488.64</v>
+        <v>17.25</v>
       </c>
       <c r="E18" t="n">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="F18" t="n">
-        <v>584</v>
+        <v>1619</v>
       </c>
       <c r="G18" t="n">
-        <v>227.12</v>
+        <v>316.88</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1221</v>
+      </c>
+      <c r="L18" t="n">
+        <v>128</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.66</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:19.085</t>
+          <t>2026-05-29 09:43:49.389</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779504974693</v>
+        <v>1780022628365</v>
       </c>
       <c r="C19" t="n">
-        <v>94687</v>
+        <v>82456</v>
       </c>
       <c r="D19" t="n">
-        <v>1278.21</v>
+        <v>92.39</v>
       </c>
       <c r="E19" t="n">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="F19" t="n">
-        <v>584</v>
+        <v>1619</v>
       </c>
       <c r="G19" t="n">
-        <v>227.12</v>
+        <v>316.88</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I19" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1023</v>
+      </c>
+      <c r="L19" t="n">
+        <v>106</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.159</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:19.892</t>
+          <t>2026-05-29 09:43:50.219</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779504974894</v>
+        <v>1780022628584</v>
       </c>
       <c r="C20" t="n">
-        <v>94787</v>
+        <v>83553</v>
       </c>
       <c r="D20" t="n">
-        <v>1314.3</v>
+        <v>1184.77</v>
       </c>
       <c r="E20" t="n">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="F20" t="n">
-        <v>584</v>
+        <v>1619</v>
       </c>
       <c r="G20" t="n">
-        <v>227.12</v>
+        <v>316.88</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1634</v>
+      </c>
+      <c r="L20" t="n">
+        <v>132</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.9360000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:19.898</t>
+          <t>2026-05-29 09:43:50.236</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779504975095</v>
+        <v>1780022628784</v>
       </c>
       <c r="C21" t="n">
-        <v>94844</v>
+        <v>83348</v>
       </c>
       <c r="D21" t="n">
-        <v>1305.58</v>
+        <v>920.53</v>
       </c>
       <c r="E21" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F21" t="n">
-        <v>1468</v>
+        <v>1619</v>
       </c>
       <c r="G21" t="n">
-        <v>396.09</v>
+        <v>316.88</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1452</v>
+      </c>
+      <c r="L21" t="n">
+        <v>108</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.827</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:20.179</t>
+          <t>2026-05-29 09:43:50.238</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1779504975297</v>
+        <v>1780022628984</v>
       </c>
       <c r="C22" t="n">
-        <v>94824</v>
+        <v>83310</v>
       </c>
       <c r="D22" t="n">
-        <v>1220.3</v>
+        <v>836.5</v>
       </c>
       <c r="E22" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F22" t="n">
-        <v>1468</v>
+        <v>1619</v>
       </c>
       <c r="G22" t="n">
-        <v>396.09</v>
+        <v>316.88</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1253</v>
+      </c>
+      <c r="L22" t="n">
+        <v>138</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.466</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:20.182</t>
+          <t>2026-05-29 09:43:50.406</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1779504975498</v>
+        <v>1780022629184</v>
       </c>
       <c r="C23" t="n">
-        <v>94640</v>
+        <v>84037</v>
       </c>
       <c r="D23" t="n">
-        <v>975.29</v>
+        <v>1521.68</v>
       </c>
       <c r="E23" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F23" t="n">
-        <v>1468</v>
+        <v>1619</v>
       </c>
       <c r="G23" t="n">
-        <v>396.09</v>
+        <v>316.88</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1221</v>
+      </c>
+      <c r="L23" t="n">
+        <v>119</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.027</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:20.188</t>
+          <t>2026-05-29 09:43:50.408</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1779504975699</v>
+        <v>1780022629384</v>
       </c>
       <c r="C24" t="n">
-        <v>94670</v>
+        <v>83719</v>
       </c>
       <c r="D24" t="n">
-        <v>956.52</v>
+        <v>1127.59</v>
       </c>
       <c r="E24" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F24" t="n">
-        <v>1468</v>
+        <v>1619</v>
       </c>
       <c r="G24" t="n">
-        <v>396.09</v>
+        <v>316.88</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1023</v>
+      </c>
+      <c r="L24" t="n">
+        <v>108</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.793</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:20.216</t>
+          <t>2026-05-29 09:43:50.408</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1779504975900</v>
+        <v>1780022629584</v>
       </c>
       <c r="C25" t="n">
-        <v>94738</v>
+        <v>83134</v>
       </c>
       <c r="D25" t="n">
-        <v>976.7</v>
+        <v>486.21</v>
       </c>
       <c r="E25" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F25" t="n">
-        <v>1468</v>
+        <v>1619</v>
       </c>
       <c r="G25" t="n">
-        <v>396.09</v>
+        <v>316.88</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K25" t="n">
+        <v>824</v>
+      </c>
+      <c r="L25" t="n">
+        <v>140</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.639</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:20.755</t>
+          <t>2026-05-29 09:43:52.623</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1779504976101</v>
+        <v>1780022629784</v>
       </c>
       <c r="C26" t="n">
-        <v>94712</v>
+        <v>83681</v>
       </c>
       <c r="D26" t="n">
-        <v>901.86</v>
+        <v>1008.9</v>
       </c>
       <c r="E26" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="F26" t="n">
-        <v>946</v>
+        <v>1619</v>
       </c>
       <c r="G26" t="n">
-        <v>356.3</v>
+        <v>316.88</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2839</v>
+      </c>
+      <c r="L26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.631</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:20.758</t>
+          <t>2026-05-29 09:43:52.624</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1779504976303</v>
+        <v>1780022630003</v>
       </c>
       <c r="C27" t="n">
-        <v>94605</v>
+        <v>84030</v>
       </c>
       <c r="D27" t="n">
-        <v>749.77</v>
+        <v>1307.46</v>
       </c>
       <c r="E27" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="F27" t="n">
-        <v>946</v>
+        <v>1619</v>
       </c>
       <c r="G27" t="n">
-        <v>356.3</v>
+        <v>316.88</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2621</v>
+      </c>
+      <c r="L27" t="n">
+        <v>112</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.586</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:21.021</t>
+          <t>2026-05-29 09:43:52.626</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1779504976504</v>
+        <v>1780022630203</v>
       </c>
       <c r="C28" t="n">
-        <v>94663</v>
+        <v>83582</v>
       </c>
       <c r="D28" t="n">
-        <v>770.28</v>
+        <v>794.09</v>
       </c>
       <c r="E28" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="F28" t="n">
-        <v>946</v>
+        <v>1619</v>
       </c>
       <c r="G28" t="n">
-        <v>356.3</v>
+        <v>316.88</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J28" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2422</v>
+      </c>
+      <c r="L28" t="n">
+        <v>113</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.157</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:21.070</t>
+          <t>2026-05-29 09:43:52.629</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1779504976705</v>
+        <v>1780022630403</v>
       </c>
       <c r="C29" t="n">
-        <v>94887</v>
+        <v>83616</v>
       </c>
       <c r="D29" t="n">
-        <v>955.77</v>
+        <v>788.38</v>
       </c>
       <c r="E29" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="F29" t="n">
-        <v>684</v>
+        <v>1619</v>
       </c>
       <c r="G29" t="n">
-        <v>332.65</v>
+        <v>316.88</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J29" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2224</v>
+      </c>
+      <c r="L29" t="n">
+        <v>110</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.398</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:21.427</t>
+          <t>2026-05-29 09:43:52.641</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1779504976906</v>
+        <v>1780022630603</v>
       </c>
       <c r="C30" t="n">
-        <v>94734</v>
+        <v>83252</v>
       </c>
       <c r="D30" t="n">
-        <v>754.98</v>
+        <v>384.96</v>
       </c>
       <c r="E30" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="F30" t="n">
-        <v>684</v>
+        <v>1619</v>
       </c>
       <c r="G30" t="n">
-        <v>332.65</v>
+        <v>316.88</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2037</v>
+      </c>
+      <c r="L30" t="n">
+        <v>113</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.147</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:21.430</t>
+          <t>2026-05-29 09:43:52.671</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1779504977107</v>
+        <v>1780022630803</v>
       </c>
       <c r="C31" t="n">
-        <v>94789</v>
+        <v>85077</v>
       </c>
       <c r="D31" t="n">
-        <v>772.23</v>
+        <v>2190.71</v>
       </c>
       <c r="E31" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="F31" t="n">
-        <v>684</v>
+        <v>3718</v>
       </c>
       <c r="G31" t="n">
-        <v>332.65</v>
+        <v>316.88</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1867</v>
+      </c>
+      <c r="L31" t="n">
+        <v>112</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.381</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:22.409</t>
+          <t>2026-05-29 09:43:52.804</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1779504977308</v>
+        <v>1780022631003</v>
       </c>
       <c r="C32" t="n">
-        <v>94938</v>
+        <v>83337</v>
       </c>
       <c r="D32" t="n">
-        <v>882.62</v>
+        <v>341.18</v>
       </c>
       <c r="E32" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="F32" t="n">
-        <v>684</v>
+        <v>3718</v>
       </c>
       <c r="G32" t="n">
-        <v>332.65</v>
+        <v>316.88</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I32" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1799</v>
+      </c>
+      <c r="L32" t="n">
+        <v>114</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.777</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:22.513</t>
+          <t>2026-05-29 09:43:52.806</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1779504977510</v>
+        <v>1780022631203</v>
       </c>
       <c r="C33" t="n">
-        <v>94959</v>
+        <v>83723</v>
       </c>
       <c r="D33" t="n">
-        <v>859.49</v>
+        <v>710.12</v>
       </c>
       <c r="E33" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="F33" t="n">
-        <v>684</v>
+        <v>3718</v>
       </c>
       <c r="G33" t="n">
-        <v>332.65</v>
+        <v>316.88</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1601</v>
+      </c>
+      <c r="L33" t="n">
+        <v>115</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.53</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:22.527</t>
+          <t>2026-05-29 09:43:52.808</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1779504977711</v>
+        <v>1780022631403</v>
       </c>
       <c r="C34" t="n">
-        <v>94734</v>
+        <v>83568</v>
       </c>
       <c r="D34" t="n">
-        <v>591.51</v>
+        <v>519.61</v>
       </c>
       <c r="E34" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="F34" t="n">
-        <v>684</v>
+        <v>3718</v>
       </c>
       <c r="G34" t="n">
-        <v>332.65</v>
+        <v>316.88</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1403</v>
+      </c>
+      <c r="L34" t="n">
+        <v>109</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.864</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:22.528</t>
+          <t>2026-05-29 09:43:52.810</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1779504977912</v>
+        <v>1780022631603</v>
       </c>
       <c r="C35" t="n">
-        <v>94810</v>
+        <v>84732</v>
       </c>
       <c r="D35" t="n">
-        <v>637.9400000000001</v>
+        <v>1657.63</v>
       </c>
       <c r="E35" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="F35" t="n">
-        <v>684</v>
+        <v>3718</v>
       </c>
       <c r="G35" t="n">
-        <v>332.65</v>
+        <v>316.88</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1205</v>
+      </c>
+      <c r="L35" t="n">
+        <v>113</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.818</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:22.547</t>
+          <t>2026-05-29 09:43:52.982</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1779504978113</v>
+        <v>1780022631822</v>
       </c>
       <c r="C36" t="n">
-        <v>94917</v>
+        <v>84278</v>
       </c>
       <c r="D36" t="n">
-        <v>713.04</v>
+        <v>1120.75</v>
       </c>
       <c r="E36" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="F36" t="n">
-        <v>684</v>
+        <v>3718</v>
       </c>
       <c r="G36" t="n">
-        <v>332.65</v>
+        <v>316.88</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1159</v>
+      </c>
+      <c r="L36" t="n">
+        <v>113</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.379</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:22.665</t>
+          <t>2026-05-29 09:43:53.025</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1779504978314</v>
+        <v>1780022632022</v>
       </c>
       <c r="C37" t="n">
-        <v>94696</v>
+        <v>83366</v>
       </c>
       <c r="D37" t="n">
-        <v>456.39</v>
+        <v>152.71</v>
       </c>
       <c r="E37" t="n">
         <v>57</v>
       </c>
       <c r="F37" t="n">
-        <v>1488</v>
+        <v>3718</v>
       </c>
       <c r="G37" t="n">
-        <v>383.39</v>
+        <v>316.88</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I37" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1002</v>
+      </c>
+      <c r="L37" t="n">
+        <v>114</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.735</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:23.091</t>
+          <t>2026-05-29 09:43:53.208</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1779504978515</v>
+        <v>1780022632222</v>
       </c>
       <c r="C38" t="n">
-        <v>94772</v>
+        <v>83370</v>
       </c>
       <c r="D38" t="n">
-        <v>509.57</v>
+        <v>149.08</v>
       </c>
       <c r="E38" t="n">
         <v>57</v>
       </c>
       <c r="F38" t="n">
-        <v>1488</v>
+        <v>3718</v>
       </c>
       <c r="G38" t="n">
-        <v>383.39</v>
+        <v>316.88</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J38" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K38" t="n">
+        <v>984</v>
+      </c>
+      <c r="L38" t="n">
+        <v>118</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.391</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:23.093</t>
+          <t>2026-05-29 09:43:53.210</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1779504978717</v>
+        <v>1780022632422</v>
       </c>
       <c r="C39" t="n">
-        <v>94840</v>
+        <v>82859</v>
       </c>
       <c r="D39" t="n">
-        <v>552.09</v>
+        <v>-369.38</v>
       </c>
       <c r="E39" t="n">
         <v>57</v>
       </c>
       <c r="F39" t="n">
-        <v>1488</v>
+        <v>3718</v>
       </c>
       <c r="G39" t="n">
-        <v>383.39</v>
+        <v>316.88</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K39" t="n">
+        <v>786</v>
+      </c>
+      <c r="L39" t="n">
+        <v>109</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.203</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:23.706</t>
+          <t>2026-05-29 09:43:53.815</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1779504978918</v>
+        <v>1780022632622</v>
       </c>
       <c r="C40" t="n">
-        <v>94929</v>
+        <v>82690</v>
       </c>
       <c r="D40" t="n">
-        <v>613.49</v>
+        <v>-519.91</v>
       </c>
       <c r="E40" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F40" t="n">
-        <v>644</v>
+        <v>3718</v>
       </c>
       <c r="G40" t="n">
-        <v>370.48</v>
+        <v>316.88</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1191</v>
+      </c>
+      <c r="L40" t="n">
+        <v>109</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.612</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:23.707</t>
+          <t>2026-05-29 09:43:53.816</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1779504979119</v>
+        <v>1780022632822</v>
       </c>
       <c r="C41" t="n">
-        <v>94725</v>
+        <v>82774</v>
       </c>
       <c r="D41" t="n">
-        <v>378.81</v>
+        <v>-409.91</v>
       </c>
       <c r="E41" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F41" t="n">
-        <v>644</v>
+        <v>3718</v>
       </c>
       <c r="G41" t="n">
-        <v>370.48</v>
+        <v>316.88</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K41" t="n">
+        <v>993</v>
+      </c>
+      <c r="L41" t="n">
+        <v>109</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.862</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:24.233</t>
+          <t>2026-05-29 09:43:54.112</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1779504979320</v>
+        <v>1780022633022</v>
       </c>
       <c r="C42" t="n">
-        <v>94886</v>
+        <v>83546</v>
       </c>
       <c r="D42" t="n">
-        <v>520.87</v>
+        <v>382.58</v>
       </c>
       <c r="E42" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F42" t="n">
-        <v>644</v>
+        <v>3718</v>
       </c>
       <c r="G42" t="n">
-        <v>370.48</v>
+        <v>316.88</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1089</v>
+      </c>
+      <c r="L42" t="n">
+        <v>124</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.921</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:24.522</t>
+          <t>2026-05-29 09:43:54.122</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1779504979521</v>
+        <v>1780022633241</v>
       </c>
       <c r="C43" t="n">
-        <v>95006</v>
+        <v>85228</v>
       </c>
       <c r="D43" t="n">
-        <v>614.83</v>
+        <v>2045.45</v>
       </c>
       <c r="E43" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="F43" t="n">
-        <v>644</v>
+        <v>3718</v>
       </c>
       <c r="G43" t="n">
-        <v>357.98</v>
+        <v>316.88</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J43" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K43" t="n">
+        <v>880</v>
+      </c>
+      <c r="L43" t="n">
+        <v>109</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.084</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:24.523</t>
+          <t>2026-05-29 09:43:54.512</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1779504979722</v>
+        <v>1780022633441</v>
       </c>
       <c r="C44" t="n">
-        <v>95085</v>
+        <v>84304</v>
       </c>
       <c r="D44" t="n">
-        <v>663.09</v>
+        <v>1019.18</v>
       </c>
       <c r="E44" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="F44" t="n">
-        <v>644</v>
+        <v>3718</v>
       </c>
       <c r="G44" t="n">
-        <v>357.98</v>
+        <v>316.88</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I44" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J44" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1070</v>
+      </c>
+      <c r="L44" t="n">
+        <v>114</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.264</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:24.524</t>
+          <t>2026-05-29 09:43:54.566</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1779504979924</v>
+        <v>1780022633641</v>
       </c>
       <c r="C45" t="n">
-        <v>94890</v>
+        <v>83870</v>
       </c>
       <c r="D45" t="n">
-        <v>434.93</v>
+        <v>534.22</v>
       </c>
       <c r="E45" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="F45" t="n">
-        <v>644</v>
+        <v>3718</v>
       </c>
       <c r="G45" t="n">
-        <v>357.98</v>
+        <v>316.88</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J45" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K45" t="n">
+        <v>924</v>
+      </c>
+      <c r="L45" t="n">
+        <v>114</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.239</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:24.916</t>
+          <t>2026-05-29 09:43:54.886</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1779504980125</v>
+        <v>1780022633841</v>
       </c>
       <c r="C46" t="n">
-        <v>94949</v>
+        <v>84545</v>
       </c>
       <c r="D46" t="n">
-        <v>472.19</v>
+        <v>1182.51</v>
       </c>
       <c r="E46" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="F46" t="n">
-        <v>644</v>
+        <v>3718</v>
       </c>
       <c r="G46" t="n">
-        <v>357.98</v>
+        <v>316.88</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I46" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1043</v>
+      </c>
+      <c r="L46" t="n">
+        <v>123</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.399</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:24.950</t>
+          <t>2026-05-29 09:43:54.887</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1779504980326</v>
+        <v>1780022634041</v>
       </c>
       <c r="C47" t="n">
-        <v>95024</v>
+        <v>85355</v>
       </c>
       <c r="D47" t="n">
-        <v>523.58</v>
+        <v>1933.39</v>
       </c>
       <c r="E47" t="n">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="F47" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G47" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J47" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K47" t="n">
         <v>845</v>
       </c>
-      <c r="G47" t="n">
-        <v>332.2</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
+      <c r="L47" t="n">
+        <v>115</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.944</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-23 09:56:25.325</t>
+          <t>2026-05-29 09:43:55.337</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1779504980527</v>
+        <v>1780022634241</v>
       </c>
       <c r="C48" t="n">
-        <v>94962</v>
+        <v>85742</v>
       </c>
       <c r="D48" t="n">
-        <v>435.4</v>
+        <v>2223.72</v>
       </c>
       <c r="E48" t="n">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="F48" t="n">
-        <v>845</v>
+        <v>3718</v>
       </c>
       <c r="G48" t="n">
-        <v>332.2</v>
+        <v>316.88</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J48" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1095</v>
+      </c>
+      <c r="L48" t="n">
+        <v>114</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.049</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:55.339</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1780022634441</v>
+      </c>
+      <c r="C49" t="n">
+        <v>85735</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2105.53</v>
+      </c>
+      <c r="E49" t="n">
+        <v>57</v>
+      </c>
+      <c r="F49" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G49" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J49" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K49" t="n">
+        <v>897</v>
+      </c>
+      <c r="L49" t="n">
+        <v>111</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.081</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:55.718</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1780022634641</v>
+      </c>
+      <c r="C50" t="n">
+        <v>86553</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2818.25</v>
+      </c>
+      <c r="E50" t="n">
+        <v>57</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G50" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1075</v>
+      </c>
+      <c r="L50" t="n">
+        <v>105</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.511</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:55.719</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1780022634860</v>
+      </c>
+      <c r="C51" t="n">
+        <v>86308</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2432.34</v>
+      </c>
+      <c r="E51" t="n">
+        <v>57</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G51" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J51" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K51" t="n">
+        <v>858</v>
+      </c>
+      <c r="L51" t="n">
+        <v>108</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.899</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:56.306</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1780022635060</v>
+      </c>
+      <c r="C52" t="n">
+        <v>86090</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2092.72</v>
+      </c>
+      <c r="E52" t="n">
+        <v>57</v>
+      </c>
+      <c r="F52" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G52" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J52" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1245</v>
+      </c>
+      <c r="L52" t="n">
+        <v>111</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.668</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:56.311</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1780022635260</v>
+      </c>
+      <c r="C53" t="n">
+        <v>86274</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2172.09</v>
+      </c>
+      <c r="E53" t="n">
+        <v>57</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G53" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1051</v>
+      </c>
+      <c r="L53" t="n">
+        <v>111</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:56.716</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1780022635460</v>
+      </c>
+      <c r="C54" t="n">
+        <v>88466</v>
+      </c>
+      <c r="D54" t="n">
+        <v>4255.48</v>
+      </c>
+      <c r="E54" t="n">
+        <v>57</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G54" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="J54" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1254</v>
+      </c>
+      <c r="L54" t="n">
+        <v>108</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.184</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:56.717</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1780022635660</v>
+      </c>
+      <c r="C55" t="n">
+        <v>87119</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2695.71</v>
+      </c>
+      <c r="E55" t="n">
+        <v>57</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G55" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1056</v>
+      </c>
+      <c r="L55" t="n">
+        <v>115</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.869</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:57.195</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1780022635861</v>
+      </c>
+      <c r="C56" t="n">
+        <v>85314</v>
+      </c>
+      <c r="D56" t="n">
+        <v>755.92</v>
+      </c>
+      <c r="E56" t="n">
+        <v>57</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G56" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1333</v>
+      </c>
+      <c r="L56" t="n">
+        <v>112</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.596</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:57.196</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1780022636060</v>
+      </c>
+      <c r="C57" t="n">
+        <v>85190</v>
+      </c>
+      <c r="D57" t="n">
+        <v>594.13</v>
+      </c>
+      <c r="E57" t="n">
+        <v>57</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G57" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1135</v>
+      </c>
+      <c r="L57" t="n">
+        <v>110</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.521</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:57.776</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1780022636279</v>
+      </c>
+      <c r="C58" t="n">
+        <v>85082</v>
+      </c>
+      <c r="D58" t="n">
+        <v>456.42</v>
+      </c>
+      <c r="E58" t="n">
+        <v>57</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G58" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1496</v>
+      </c>
+      <c r="L58" t="n">
+        <v>109</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.078</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:57.798</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1780022636479</v>
+      </c>
+      <c r="C59" t="n">
+        <v>85295</v>
+      </c>
+      <c r="D59" t="n">
+        <v>646.6</v>
+      </c>
+      <c r="E59" t="n">
+        <v>57</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G59" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J59" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1317</v>
+      </c>
+      <c r="L59" t="n">
+        <v>116</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.895</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:57.800</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1780022636679</v>
+      </c>
+      <c r="C60" t="n">
+        <v>85337</v>
+      </c>
+      <c r="D60" t="n">
+        <v>656.27</v>
+      </c>
+      <c r="E60" t="n">
+        <v>57</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G60" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J60" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1120</v>
+      </c>
+      <c r="L60" t="n">
+        <v>129</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:58.060</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1780022636879</v>
+      </c>
+      <c r="C61" t="n">
+        <v>85289</v>
+      </c>
+      <c r="D61" t="n">
+        <v>575.46</v>
+      </c>
+      <c r="E61" t="n">
+        <v>57</v>
+      </c>
+      <c r="F61" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G61" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="J61" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1180</v>
+      </c>
+      <c r="L61" t="n">
+        <v>106</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.349</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:58.088</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1780022637079</v>
+      </c>
+      <c r="C62" t="n">
+        <v>84736</v>
+      </c>
+      <c r="D62" t="n">
+        <v>-6.32</v>
+      </c>
+      <c r="E62" t="n">
+        <v>57</v>
+      </c>
+      <c r="F62" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G62" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J62" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1008</v>
+      </c>
+      <c r="L62" t="n">
+        <v>107</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.705</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:58.410</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1780022637279</v>
+      </c>
+      <c r="C63" t="n">
+        <v>84642</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-100</v>
+      </c>
+      <c r="E63" t="n">
+        <v>57</v>
+      </c>
+      <c r="F63" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G63" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J63" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1130</v>
+      </c>
+      <c r="L63" t="n">
+        <v>114</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.642</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:58.412</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1780022637479</v>
+      </c>
+      <c r="C64" t="n">
+        <v>84492</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-245</v>
+      </c>
+      <c r="E64" t="n">
+        <v>57</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G64" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J64" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K64" t="n">
+        <v>932</v>
+      </c>
+      <c r="L64" t="n">
+        <v>133</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:58.766</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1780022637679</v>
+      </c>
+      <c r="C65" t="n">
+        <v>84145</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-579.75</v>
+      </c>
+      <c r="E65" t="n">
+        <v>57</v>
+      </c>
+      <c r="F65" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G65" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J65" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1085</v>
+      </c>
+      <c r="L65" t="n">
+        <v>113</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.647</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:58.767</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1780022637898</v>
+      </c>
+      <c r="C66" t="n">
+        <v>84115</v>
+      </c>
+      <c r="D66" t="n">
+        <v>-580.76</v>
+      </c>
+      <c r="E66" t="n">
+        <v>57</v>
+      </c>
+      <c r="F66" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G66" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K66" t="n">
+        <v>868</v>
+      </c>
+      <c r="L66" t="n">
+        <v>117</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.155</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:59.277</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1780022638098</v>
+      </c>
+      <c r="C67" t="n">
+        <v>84114</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-552.72</v>
+      </c>
+      <c r="E67" t="n">
+        <v>57</v>
+      </c>
+      <c r="F67" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G67" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1178</v>
+      </c>
+      <c r="L67" t="n">
+        <v>123</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.847</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:59.278</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1780022638298</v>
+      </c>
+      <c r="C68" t="n">
+        <v>84031</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-608.09</v>
+      </c>
+      <c r="E68" t="n">
+        <v>57</v>
+      </c>
+      <c r="F68" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G68" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J68" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K68" t="n">
+        <v>979</v>
+      </c>
+      <c r="L68" t="n">
+        <v>114</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.539</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:59.279</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1780022638498</v>
+      </c>
+      <c r="C69" t="n">
+        <v>83711</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-897.6799999999999</v>
+      </c>
+      <c r="E69" t="n">
+        <v>57</v>
+      </c>
+      <c r="F69" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G69" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K69" t="n">
+        <v>780</v>
+      </c>
+      <c r="L69" t="n">
+        <v>118</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.788</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:43:59.568</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1780022638698</v>
+      </c>
+      <c r="C70" t="n">
+        <v>84010</v>
+      </c>
+      <c r="D70" t="n">
+        <v>-553.8</v>
+      </c>
+      <c r="E70" t="n">
+        <v>57</v>
+      </c>
+      <c r="F70" t="n">
+        <v>3718</v>
+      </c>
+      <c r="G70" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J70" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K70" t="n">
+        <v>869</v>
+      </c>
+      <c r="L70" t="n">
+        <v>122</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.437</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:00.006</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1780022638898</v>
+      </c>
+      <c r="C71" t="n">
+        <v>84463</v>
+      </c>
+      <c r="D71" t="n">
+        <v>-73.11</v>
+      </c>
+      <c r="E71" t="n">
+        <v>57</v>
+      </c>
+      <c r="F71" t="n">
+        <v>8075</v>
+      </c>
+      <c r="G71" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J71" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1107</v>
+      </c>
+      <c r="L71" t="n">
+        <v>116</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.982</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:00.007</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1780022639098</v>
+      </c>
+      <c r="C72" t="n">
+        <v>84344</v>
+      </c>
+      <c r="D72" t="n">
+        <v>-188.45</v>
+      </c>
+      <c r="E72" t="n">
+        <v>57</v>
+      </c>
+      <c r="F72" t="n">
+        <v>8075</v>
+      </c>
+      <c r="G72" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J72" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K72" t="n">
+        <v>908</v>
+      </c>
+      <c r="L72" t="n">
+        <v>113</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.743</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:00.485</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1780022639317</v>
+      </c>
+      <c r="C73" t="n">
+        <v>84011</v>
+      </c>
+      <c r="D73" t="n">
+        <v>-512.03</v>
+      </c>
+      <c r="E73" t="n">
+        <v>57</v>
+      </c>
+      <c r="F73" t="n">
+        <v>8075</v>
+      </c>
+      <c r="G73" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J73" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1167</v>
+      </c>
+      <c r="L73" t="n">
+        <v>119</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1.254</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:00.487</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1780022639517</v>
+      </c>
+      <c r="C74" t="n">
+        <v>83951</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-546.4299999999999</v>
+      </c>
+      <c r="E74" t="n">
+        <v>57</v>
+      </c>
+      <c r="F74" t="n">
+        <v>8075</v>
+      </c>
+      <c r="G74" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K74" t="n">
+        <v>968</v>
+      </c>
+      <c r="L74" t="n">
+        <v>118</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1.365</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:00.835</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1780022639717</v>
+      </c>
+      <c r="C75" t="n">
+        <v>83968</v>
+      </c>
+      <c r="D75" t="n">
+        <v>-502.11</v>
+      </c>
+      <c r="E75" t="n">
+        <v>57</v>
+      </c>
+      <c r="F75" t="n">
+        <v>8075</v>
+      </c>
+      <c r="G75" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1117</v>
+      </c>
+      <c r="L75" t="n">
+        <v>120</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.444</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:00.851</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1780022639917</v>
+      </c>
+      <c r="C76" t="n">
+        <v>83726</v>
+      </c>
+      <c r="D76" t="n">
+        <v>-719</v>
+      </c>
+      <c r="E76" t="n">
+        <v>57</v>
+      </c>
+      <c r="F76" t="n">
+        <v>8075</v>
+      </c>
+      <c r="G76" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K76" t="n">
+        <v>932</v>
+      </c>
+      <c r="L76" t="n">
+        <v>114</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1.679</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:01.233</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1780022640118</v>
+      </c>
+      <c r="C77" t="n">
+        <v>83695</v>
+      </c>
+      <c r="D77" t="n">
+        <v>-714.05</v>
+      </c>
+      <c r="E77" t="n">
+        <v>57</v>
+      </c>
+      <c r="F77" t="n">
+        <v>8075</v>
+      </c>
+      <c r="G77" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.67</v>
+      </c>
+      <c r="J77" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1114</v>
+      </c>
+      <c r="L77" t="n">
+        <v>106</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.727</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:01.242</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1780022640317</v>
+      </c>
+      <c r="C78" t="n">
+        <v>83780</v>
+      </c>
+      <c r="D78" t="n">
+        <v>-593.35</v>
+      </c>
+      <c r="E78" t="n">
+        <v>57</v>
+      </c>
+      <c r="F78" t="n">
+        <v>8075</v>
+      </c>
+      <c r="G78" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J78" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K78" t="n">
+        <v>924</v>
+      </c>
+      <c r="L78" t="n">
+        <v>108</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.749</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:01.659</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1780022640518</v>
+      </c>
+      <c r="C79" t="n">
+        <v>83595</v>
+      </c>
+      <c r="D79" t="n">
+        <v>-748.6799999999999</v>
+      </c>
+      <c r="E79" t="n">
+        <v>57</v>
+      </c>
+      <c r="F79" t="n">
+        <v>8075</v>
+      </c>
+      <c r="G79" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="J79" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1140</v>
+      </c>
+      <c r="L79" t="n">
+        <v>107</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.097</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:01.660</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1780022640717</v>
+      </c>
+      <c r="C80" t="n">
+        <v>83332</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-974.25</v>
+      </c>
+      <c r="E80" t="n">
+        <v>57</v>
+      </c>
+      <c r="F80" t="n">
+        <v>8075</v>
+      </c>
+      <c r="G80" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="J80" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K80" t="n">
+        <v>942</v>
+      </c>
+      <c r="L80" t="n">
+        <v>107</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.782</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:02.064</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1780022640937</v>
+      </c>
+      <c r="C81" t="n">
+        <v>83457</v>
+      </c>
+      <c r="D81" t="n">
+        <v>-800.54</v>
+      </c>
+      <c r="E81" t="n">
+        <v>57</v>
+      </c>
+      <c r="F81" t="n">
+        <v>8075</v>
+      </c>
+      <c r="G81" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.54</v>
+      </c>
+      <c r="J81" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1126</v>
+      </c>
+      <c r="L81" t="n">
+        <v>106</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.534</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:02.106</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1780022641136</v>
+      </c>
+      <c r="C82" t="n">
+        <v>83541</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-676.51</v>
+      </c>
+      <c r="E82" t="n">
+        <v>57</v>
+      </c>
+      <c r="F82" t="n">
+        <v>8075</v>
+      </c>
+      <c r="G82" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K82" t="n">
+        <v>969</v>
+      </c>
+      <c r="L82" t="n">
+        <v>112</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1.125</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:02.545</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1780022641337</v>
+      </c>
+      <c r="C83" t="n">
+        <v>83171</v>
+      </c>
+      <c r="D83" t="n">
+        <v>-1012.68</v>
+      </c>
+      <c r="E83" t="n">
+        <v>57</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2358</v>
+      </c>
+      <c r="G83" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.54</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1207</v>
+      </c>
+      <c r="L83" t="n">
+        <v>108</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:02.547</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1780022641536</v>
+      </c>
+      <c r="C84" t="n">
+        <v>83144</v>
+      </c>
+      <c r="D84" t="n">
+        <v>-989.05</v>
+      </c>
+      <c r="E84" t="n">
+        <v>57</v>
+      </c>
+      <c r="F84" t="n">
+        <v>2358</v>
+      </c>
+      <c r="G84" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="J84" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1010</v>
+      </c>
+      <c r="L84" t="n">
+        <v>107</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.746</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:02.549</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1780022641737</v>
+      </c>
+      <c r="C85" t="n">
+        <v>83111</v>
+      </c>
+      <c r="D85" t="n">
+        <v>-972.6</v>
+      </c>
+      <c r="E85" t="n">
+        <v>57</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2358</v>
+      </c>
+      <c r="G85" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>49.97</v>
+      </c>
+      <c r="J85" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K85" t="n">
+        <v>811</v>
+      </c>
+      <c r="L85" t="n">
+        <v>104</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.916</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:02.947</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1780022641936</v>
+      </c>
+      <c r="C86" t="n">
+        <v>83028</v>
+      </c>
+      <c r="D86" t="n">
+        <v>-1006.97</v>
+      </c>
+      <c r="E86" t="n">
+        <v>57</v>
+      </c>
+      <c r="F86" t="n">
+        <v>2358</v>
+      </c>
+      <c r="G86" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1009</v>
+      </c>
+      <c r="L86" t="n">
+        <v>121</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.236</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:03.591</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1780022642136</v>
+      </c>
+      <c r="C87" t="n">
+        <v>82866</v>
+      </c>
+      <c r="D87" t="n">
+        <v>-1118.62</v>
+      </c>
+      <c r="E87" t="n">
+        <v>57</v>
+      </c>
+      <c r="F87" t="n">
+        <v>2358</v>
+      </c>
+      <c r="G87" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J87" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1454</v>
+      </c>
+      <c r="L87" t="n">
+        <v>115</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.244</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:03.593</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1780022642336</v>
+      </c>
+      <c r="C88" t="n">
+        <v>82912</v>
+      </c>
+      <c r="D88" t="n">
+        <v>-1016.69</v>
+      </c>
+      <c r="E88" t="n">
+        <v>57</v>
+      </c>
+      <c r="F88" t="n">
+        <v>2358</v>
+      </c>
+      <c r="G88" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J88" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1256</v>
+      </c>
+      <c r="L88" t="n">
+        <v>108</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.073</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:03.594</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1780022642556</v>
+      </c>
+      <c r="C89" t="n">
+        <v>82983</v>
+      </c>
+      <c r="D89" t="n">
+        <v>-894.85</v>
+      </c>
+      <c r="E89" t="n">
+        <v>57</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2358</v>
+      </c>
+      <c r="G89" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1037</v>
+      </c>
+      <c r="L89" t="n">
+        <v>108</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.284</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:04.672</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1780022642755</v>
+      </c>
+      <c r="C90" t="n">
+        <v>82812</v>
+      </c>
+      <c r="D90" t="n">
+        <v>-1021.11</v>
+      </c>
+      <c r="E90" t="n">
+        <v>50</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1399</v>
+      </c>
+      <c r="G90" t="n">
+        <v>333.72</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="J90" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1916</v>
+      </c>
+      <c r="L90" t="n">
+        <v>107</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.665</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:04.687</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1780022642955</v>
+      </c>
+      <c r="C91" t="n">
+        <v>82956</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-826.0599999999999</v>
+      </c>
+      <c r="E91" t="n">
+        <v>50</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1399</v>
+      </c>
+      <c r="G91" t="n">
+        <v>333.72</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1731</v>
+      </c>
+      <c r="L91" t="n">
+        <v>97</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1.018</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:04.710</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1780022643155</v>
+      </c>
+      <c r="C92" t="n">
+        <v>82586</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-1154.75</v>
+      </c>
+      <c r="E92" t="n">
+        <v>73</v>
+      </c>
+      <c r="F92" t="n">
+        <v>420</v>
+      </c>
+      <c r="G92" t="n">
+        <v>315.16</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1554</v>
+      </c>
+      <c r="L92" t="n">
+        <v>117</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1.418</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:04.712</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1780022643355</v>
+      </c>
+      <c r="C93" t="n">
+        <v>83035</v>
+      </c>
+      <c r="D93" t="n">
+        <v>-648.01</v>
+      </c>
+      <c r="E93" t="n">
+        <v>73</v>
+      </c>
+      <c r="F93" t="n">
+        <v>420</v>
+      </c>
+      <c r="G93" t="n">
+        <v>315.16</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1356</v>
+      </c>
+      <c r="L93" t="n">
+        <v>104</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1.362</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:04.729</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1780022643555</v>
+      </c>
+      <c r="C94" t="n">
+        <v>83461</v>
+      </c>
+      <c r="D94" t="n">
+        <v>-189.61</v>
+      </c>
+      <c r="E94" t="n">
+        <v>89</v>
+      </c>
+      <c r="F94" t="n">
+        <v>460</v>
+      </c>
+      <c r="G94" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1172</v>
+      </c>
+      <c r="L94" t="n">
+        <v>115</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1.519</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:04.796</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1780022643755</v>
+      </c>
+      <c r="C95" t="n">
+        <v>83722</v>
+      </c>
+      <c r="D95" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="E95" t="n">
+        <v>89</v>
+      </c>
+      <c r="F95" t="n">
+        <v>460</v>
+      </c>
+      <c r="G95" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J95" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1040</v>
+      </c>
+      <c r="L95" t="n">
+        <v>105</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1.028</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:04.935</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1780022643974</v>
+      </c>
+      <c r="C96" t="n">
+        <v>83458</v>
+      </c>
+      <c r="D96" t="n">
+        <v>-187.18</v>
+      </c>
+      <c r="E96" t="n">
+        <v>89</v>
+      </c>
+      <c r="F96" t="n">
+        <v>460</v>
+      </c>
+      <c r="G96" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K96" t="n">
+        <v>960</v>
+      </c>
+      <c r="L96" t="n">
+        <v>114</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:05.046</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1780022644174</v>
+      </c>
+      <c r="C97" t="n">
+        <v>83630</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-5.82</v>
+      </c>
+      <c r="E97" t="n">
+        <v>89</v>
+      </c>
+      <c r="F97" t="n">
+        <v>460</v>
+      </c>
+      <c r="G97" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J97" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K97" t="n">
+        <v>870</v>
+      </c>
+      <c r="L97" t="n">
+        <v>105</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.642</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:05.467</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1780022644374</v>
+      </c>
+      <c r="C98" t="n">
+        <v>83668</v>
+      </c>
+      <c r="D98" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="E98" t="n">
+        <v>89</v>
+      </c>
+      <c r="F98" t="n">
+        <v>460</v>
+      </c>
+      <c r="G98" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J98" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1091</v>
+      </c>
+      <c r="L98" t="n">
+        <v>109</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.765</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:05.485</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1780022644574</v>
+      </c>
+      <c r="C99" t="n">
+        <v>83402</v>
+      </c>
+      <c r="D99" t="n">
+        <v>-235.15</v>
+      </c>
+      <c r="E99" t="n">
+        <v>89</v>
+      </c>
+      <c r="F99" t="n">
+        <v>460</v>
+      </c>
+      <c r="G99" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J99" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K99" t="n">
+        <v>910</v>
+      </c>
+      <c r="L99" t="n">
+        <v>105</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1.268</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:05.738</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1780022644774</v>
+      </c>
+      <c r="C100" t="n">
+        <v>82957</v>
+      </c>
+      <c r="D100" t="n">
+        <v>-668.39</v>
+      </c>
+      <c r="E100" t="n">
+        <v>89</v>
+      </c>
+      <c r="F100" t="n">
+        <v>460</v>
+      </c>
+      <c r="G100" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J100" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K100" t="n">
+        <v>963</v>
+      </c>
+      <c r="L100" t="n">
+        <v>110</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1.141</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:05.896</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1780022644974</v>
+      </c>
+      <c r="C101" t="n">
+        <v>83009</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-582.97</v>
+      </c>
+      <c r="E101" t="n">
+        <v>89</v>
+      </c>
+      <c r="F101" t="n">
+        <v>460</v>
+      </c>
+      <c r="G101" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J101" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K101" t="n">
+        <v>921</v>
+      </c>
+      <c r="L101" t="n">
+        <v>105</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.325</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:06.174</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1780022645174</v>
+      </c>
+      <c r="C102" t="n">
+        <v>82998</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-564.8200000000001</v>
+      </c>
+      <c r="E102" t="n">
+        <v>89</v>
+      </c>
+      <c r="F102" t="n">
+        <v>460</v>
+      </c>
+      <c r="G102" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J102" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K102" t="n">
+        <v>999</v>
+      </c>
+      <c r="L102" t="n">
+        <v>108</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.794</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:06.176</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1780022645374</v>
+      </c>
+      <c r="C103" t="n">
+        <v>82963</v>
+      </c>
+      <c r="D103" t="n">
+        <v>-571.58</v>
+      </c>
+      <c r="E103" t="n">
+        <v>89</v>
+      </c>
+      <c r="F103" t="n">
+        <v>460</v>
+      </c>
+      <c r="G103" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J103" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K103" t="n">
+        <v>801</v>
+      </c>
+      <c r="L103" t="n">
+        <v>106</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.767</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:06.609</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1780022645593</v>
+      </c>
+      <c r="C104" t="n">
+        <v>84321</v>
+      </c>
+      <c r="D104" t="n">
+        <v>815</v>
+      </c>
+      <c r="E104" t="n">
+        <v>89</v>
+      </c>
+      <c r="F104" t="n">
+        <v>2058</v>
+      </c>
+      <c r="G104" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J104" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1014</v>
+      </c>
+      <c r="L104" t="n">
+        <v>123</v>
+      </c>
+      <c r="M104" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:06.612</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1780022645793</v>
+      </c>
+      <c r="C105" t="n">
+        <v>83489</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-57.75</v>
+      </c>
+      <c r="E105" t="n">
+        <v>89</v>
+      </c>
+      <c r="F105" t="n">
+        <v>2058</v>
+      </c>
+      <c r="G105" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J105" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K105" t="n">
+        <v>817</v>
+      </c>
+      <c r="L105" t="n">
+        <v>109</v>
+      </c>
+      <c r="M105" t="n">
+        <v>1.879</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:06.983</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1780022645993</v>
+      </c>
+      <c r="C106" t="n">
+        <v>83619</v>
+      </c>
+      <c r="D106" t="n">
+        <v>75.13</v>
+      </c>
+      <c r="E106" t="n">
+        <v>89</v>
+      </c>
+      <c r="F106" t="n">
+        <v>2058</v>
+      </c>
+      <c r="G106" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J106" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K106" t="n">
+        <v>989</v>
+      </c>
+      <c r="L106" t="n">
+        <v>123</v>
+      </c>
+      <c r="M106" t="n">
+        <v>1.263</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:06.985</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1780022646193</v>
+      </c>
+      <c r="C107" t="n">
+        <v>83086</v>
+      </c>
+      <c r="D107" t="n">
+        <v>-461.62</v>
+      </c>
+      <c r="E107" t="n">
+        <v>89</v>
+      </c>
+      <c r="F107" t="n">
+        <v>2058</v>
+      </c>
+      <c r="G107" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J107" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K107" t="n">
+        <v>791</v>
+      </c>
+      <c r="L107" t="n">
+        <v>116</v>
+      </c>
+      <c r="M107" t="n">
+        <v>1.181</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:07.470</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1780022646393</v>
+      </c>
+      <c r="C108" t="n">
+        <v>82743</v>
+      </c>
+      <c r="D108" t="n">
+        <v>-781.54</v>
+      </c>
+      <c r="E108" t="n">
+        <v>89</v>
+      </c>
+      <c r="F108" t="n">
+        <v>2058</v>
+      </c>
+      <c r="G108" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J108" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1075</v>
+      </c>
+      <c r="L108" t="n">
+        <v>124</v>
+      </c>
+      <c r="M108" t="n">
+        <v>1.378</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:07.472</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1780022646593</v>
+      </c>
+      <c r="C109" t="n">
+        <v>83363</v>
+      </c>
+      <c r="D109" t="n">
+        <v>-122.46</v>
+      </c>
+      <c r="E109" t="n">
+        <v>89</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2058</v>
+      </c>
+      <c r="G109" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J109" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K109" t="n">
+        <v>877</v>
+      </c>
+      <c r="L109" t="n">
+        <v>108</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1.562</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:07.813</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1780022646793</v>
+      </c>
+      <c r="C110" t="n">
+        <v>83223</v>
+      </c>
+      <c r="D110" t="n">
+        <v>-256.34</v>
+      </c>
+      <c r="E110" t="n">
+        <v>89</v>
+      </c>
+      <c r="F110" t="n">
+        <v>2058</v>
+      </c>
+      <c r="G110" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J110" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1019</v>
+      </c>
+      <c r="L110" t="n">
+        <v>127</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1.083</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:07.816</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1780022647012</v>
+      </c>
+      <c r="C111" t="n">
+        <v>83324</v>
+      </c>
+      <c r="D111" t="n">
+        <v>-142.52</v>
+      </c>
+      <c r="E111" t="n">
+        <v>88</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1439</v>
+      </c>
+      <c r="G111" t="n">
+        <v>378.26</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="J111" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K111" t="n">
+        <v>802</v>
+      </c>
+      <c r="L111" t="n">
+        <v>116</v>
+      </c>
+      <c r="M111" t="n">
+        <v>1.218</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:08.307</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1780022647212</v>
+      </c>
+      <c r="C112" t="n">
+        <v>83836</v>
+      </c>
+      <c r="D112" t="n">
+        <v>376.6</v>
+      </c>
+      <c r="E112" t="n">
+        <v>88</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1439</v>
+      </c>
+      <c r="G112" t="n">
+        <v>378.26</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J112" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1093</v>
+      </c>
+      <c r="L112" t="n">
+        <v>117</v>
+      </c>
+      <c r="M112" t="n">
+        <v>1.445</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:08.321</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1780022647412</v>
+      </c>
+      <c r="C113" t="n">
+        <v>84119</v>
+      </c>
+      <c r="D113" t="n">
+        <v>640.77</v>
+      </c>
+      <c r="E113" t="n">
+        <v>88</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1439</v>
+      </c>
+      <c r="G113" t="n">
+        <v>378.26</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J113" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K113" t="n">
+        <v>908</v>
+      </c>
+      <c r="L113" t="n">
+        <v>114</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:08.791</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1780022647612</v>
+      </c>
+      <c r="C114" t="n">
+        <v>83724</v>
+      </c>
+      <c r="D114" t="n">
+        <v>213.73</v>
+      </c>
+      <c r="E114" t="n">
+        <v>88</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1439</v>
+      </c>
+      <c r="G114" t="n">
+        <v>378.26</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J114" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1177</v>
+      </c>
+      <c r="L114" t="n">
+        <v>118</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1.267</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:08.794</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1780022647812</v>
+      </c>
+      <c r="C115" t="n">
+        <v>84191</v>
+      </c>
+      <c r="D115" t="n">
+        <v>670.05</v>
+      </c>
+      <c r="E115" t="n">
+        <v>88</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1439</v>
+      </c>
+      <c r="G115" t="n">
+        <v>378.26</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J115" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K115" t="n">
+        <v>981</v>
+      </c>
+      <c r="L115" t="n">
+        <v>106</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0.955</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:08.998</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1780022648012</v>
+      </c>
+      <c r="C116" t="n">
+        <v>83347</v>
+      </c>
+      <c r="D116" t="n">
+        <v>-207.46</v>
+      </c>
+      <c r="E116" t="n">
+        <v>96</v>
+      </c>
+      <c r="F116" t="n">
+        <v>820</v>
+      </c>
+      <c r="G116" t="n">
+        <v>374.6</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J116" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K116" t="n">
+        <v>985</v>
+      </c>
+      <c r="L116" t="n">
+        <v>109</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0.853</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:08.999</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1780022648212</v>
+      </c>
+      <c r="C117" t="n">
+        <v>84805</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1260.92</v>
+      </c>
+      <c r="E117" t="n">
+        <v>96</v>
+      </c>
+      <c r="F117" t="n">
+        <v>820</v>
+      </c>
+      <c r="G117" t="n">
+        <v>374.6</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J117" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K117" t="n">
+        <v>786</v>
+      </c>
+      <c r="L117" t="n">
+        <v>107</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:11.585</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1780022648412</v>
+      </c>
+      <c r="C118" t="n">
+        <v>82624</v>
+      </c>
+      <c r="D118" t="n">
+        <v>-983.13</v>
+      </c>
+      <c r="E118" t="n">
+        <v>93</v>
+      </c>
+      <c r="F118" t="n">
+        <v>460</v>
+      </c>
+      <c r="G118" t="n">
+        <v>409.48</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J118" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K118" t="n">
+        <v>3172</v>
+      </c>
+      <c r="L118" t="n">
+        <v>112</v>
+      </c>
+      <c r="M118" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:11.587</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1780022648631</v>
+      </c>
+      <c r="C119" t="n">
+        <v>83540</v>
+      </c>
+      <c r="D119" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="E119" t="n">
+        <v>93</v>
+      </c>
+      <c r="F119" t="n">
+        <v>460</v>
+      </c>
+      <c r="G119" t="n">
+        <v>409.48</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J119" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K119" t="n">
+        <v>2956</v>
+      </c>
+      <c r="L119" t="n">
+        <v>104</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.753</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:11.640</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1780022648831</v>
+      </c>
+      <c r="C120" t="n">
+        <v>82999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>-558.0700000000001</v>
+      </c>
+      <c r="E120" t="n">
+        <v>93</v>
+      </c>
+      <c r="F120" t="n">
+        <v>460</v>
+      </c>
+      <c r="G120" t="n">
+        <v>409.48</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J120" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K120" t="n">
+        <v>2807</v>
+      </c>
+      <c r="L120" t="n">
+        <v>105</v>
+      </c>
+      <c r="M120" t="n">
+        <v>2.119</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:11.667</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1780022649031</v>
+      </c>
+      <c r="C121" t="n">
+        <v>83529</v>
+      </c>
+      <c r="D121" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="E121" t="n">
+        <v>93</v>
+      </c>
+      <c r="F121" t="n">
+        <v>460</v>
+      </c>
+      <c r="G121" t="n">
+        <v>409.48</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J121" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K121" t="n">
+        <v>2635</v>
+      </c>
+      <c r="L121" t="n">
+        <v>120</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.921</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:11.669</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1780022649231</v>
+      </c>
+      <c r="C122" t="n">
+        <v>83402</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-127.16</v>
+      </c>
+      <c r="E122" t="n">
+        <v>77</v>
+      </c>
+      <c r="F122" t="n">
+        <v>899</v>
+      </c>
+      <c r="G122" t="n">
+        <v>409.21</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J122" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K122" t="n">
+        <v>2437</v>
+      </c>
+      <c r="L122" t="n">
+        <v>105</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.861</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:11.671</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1780022649431</v>
+      </c>
+      <c r="C123" t="n">
+        <v>83154</v>
+      </c>
+      <c r="D123" t="n">
+        <v>-368.8</v>
+      </c>
+      <c r="E123" t="n">
+        <v>77</v>
+      </c>
+      <c r="F123" t="n">
+        <v>899</v>
+      </c>
+      <c r="G123" t="n">
+        <v>409.21</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J123" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K123" t="n">
+        <v>2238</v>
+      </c>
+      <c r="L123" t="n">
+        <v>115</v>
+      </c>
+      <c r="M123" t="n">
+        <v>1.488</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:11.672</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1780022649631</v>
+      </c>
+      <c r="C124" t="n">
+        <v>83180</v>
+      </c>
+      <c r="D124" t="n">
+        <v>-324.36</v>
+      </c>
+      <c r="E124" t="n">
+        <v>77</v>
+      </c>
+      <c r="F124" t="n">
+        <v>899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>409.21</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J124" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K124" t="n">
+        <v>2040</v>
+      </c>
+      <c r="L124" t="n">
+        <v>114</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.901</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:11.675</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1780022649831</v>
+      </c>
+      <c r="C125" t="n">
+        <v>82871</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-617.15</v>
+      </c>
+      <c r="E125" t="n">
+        <v>77</v>
+      </c>
+      <c r="F125" t="n">
+        <v>899</v>
+      </c>
+      <c r="G125" t="n">
+        <v>409.21</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J125" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1843</v>
+      </c>
+      <c r="L125" t="n">
+        <v>106</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1.013</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:11.677</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1780022650031</v>
+      </c>
+      <c r="C126" t="n">
+        <v>83431</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-26.29</v>
+      </c>
+      <c r="E126" t="n">
+        <v>77</v>
+      </c>
+      <c r="F126" t="n">
+        <v>899</v>
+      </c>
+      <c r="G126" t="n">
+        <v>409.21</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J126" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1644</v>
+      </c>
+      <c r="L126" t="n">
+        <v>108</v>
+      </c>
+      <c r="M126" t="n">
+        <v>1.755</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:11.678</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1780022650250</v>
+      </c>
+      <c r="C127" t="n">
+        <v>82710</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-745.97</v>
+      </c>
+      <c r="E127" t="n">
+        <v>84</v>
+      </c>
+      <c r="F127" t="n">
+        <v>880</v>
+      </c>
+      <c r="G127" t="n">
+        <v>399.04</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J127" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1427</v>
+      </c>
+      <c r="L127" t="n">
+        <v>118</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1.164</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:12.084</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1780022650450</v>
+      </c>
+      <c r="C128" t="n">
+        <v>83349</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-69.67</v>
+      </c>
+      <c r="E128" t="n">
+        <v>84</v>
+      </c>
+      <c r="F128" t="n">
+        <v>880</v>
+      </c>
+      <c r="G128" t="n">
+        <v>399.04</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J128" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1633</v>
+      </c>
+      <c r="L128" t="n">
+        <v>105</v>
+      </c>
+      <c r="M128" t="n">
+        <v>1.321</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:12.085</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1780022650650</v>
+      </c>
+      <c r="C129" t="n">
+        <v>82562</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-853.1900000000001</v>
+      </c>
+      <c r="E129" t="n">
+        <v>97</v>
+      </c>
+      <c r="F129" t="n">
+        <v>479</v>
+      </c>
+      <c r="G129" t="n">
+        <v>421.63</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J129" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1435</v>
+      </c>
+      <c r="L129" t="n">
+        <v>112</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.703</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:12.087</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1780022650850</v>
+      </c>
+      <c r="C130" t="n">
+        <v>83078</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-294.53</v>
+      </c>
+      <c r="E130" t="n">
+        <v>97</v>
+      </c>
+      <c r="F130" t="n">
+        <v>479</v>
+      </c>
+      <c r="G130" t="n">
+        <v>421.63</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J130" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1235</v>
+      </c>
+      <c r="L130" t="n">
+        <v>105</v>
+      </c>
+      <c r="M130" t="n">
+        <v>1.063</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:12.087</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1780022651050</v>
+      </c>
+      <c r="C131" t="n">
+        <v>82884</v>
+      </c>
+      <c r="D131" t="n">
+        <v>-473.81</v>
+      </c>
+      <c r="E131" t="n">
+        <v>97</v>
+      </c>
+      <c r="F131" t="n">
+        <v>479</v>
+      </c>
+      <c r="G131" t="n">
+        <v>421.63</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J131" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1037</v>
+      </c>
+      <c r="L131" t="n">
+        <v>117</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.769</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:12.819</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1780022651250</v>
+      </c>
+      <c r="C132" t="n">
+        <v>84261</v>
+      </c>
+      <c r="D132" t="n">
+        <v>926.89</v>
+      </c>
+      <c r="E132" t="n">
+        <v>93</v>
+      </c>
+      <c r="F132" t="n">
+        <v>520</v>
+      </c>
+      <c r="G132" t="n">
+        <v>385.25</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J132" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1568</v>
+      </c>
+      <c r="L132" t="n">
+        <v>109</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.662</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:12.845</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1780022651450</v>
+      </c>
+      <c r="C133" t="n">
+        <v>82832</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-548.46</v>
+      </c>
+      <c r="E133" t="n">
+        <v>93</v>
+      </c>
+      <c r="F133" t="n">
+        <v>520</v>
+      </c>
+      <c r="G133" t="n">
+        <v>385.25</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J133" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K133" t="n">
+        <v>1394</v>
+      </c>
+      <c r="L133" t="n">
+        <v>105</v>
+      </c>
+      <c r="M133" t="n">
+        <v>1.297</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:12.857</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>1780022651650</v>
+      </c>
+      <c r="C134" t="n">
+        <v>83979</v>
+      </c>
+      <c r="D134" t="n">
+        <v>625.96</v>
+      </c>
+      <c r="E134" t="n">
+        <v>93</v>
+      </c>
+      <c r="F134" t="n">
+        <v>520</v>
+      </c>
+      <c r="G134" t="n">
+        <v>385.25</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J134" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1205</v>
+      </c>
+      <c r="L134" t="n">
+        <v>104</v>
+      </c>
+      <c r="M134" t="n">
+        <v>1.278</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:13.175</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1780022651869</v>
+      </c>
+      <c r="C135" t="n">
+        <v>83016</v>
+      </c>
+      <c r="D135" t="n">
+        <v>-368.33</v>
+      </c>
+      <c r="E135" t="n">
+        <v>93</v>
+      </c>
+      <c r="F135" t="n">
+        <v>520</v>
+      </c>
+      <c r="G135" t="n">
+        <v>385.25</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J135" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1305</v>
+      </c>
+      <c r="L135" t="n">
+        <v>112</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.996</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:13.184</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1780022652069</v>
+      </c>
+      <c r="C136" t="n">
+        <v>83627</v>
+      </c>
+      <c r="D136" t="n">
+        <v>261.08</v>
+      </c>
+      <c r="E136" t="n">
+        <v>93</v>
+      </c>
+      <c r="F136" t="n">
+        <v>520</v>
+      </c>
+      <c r="G136" t="n">
+        <v>385.25</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J136" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1114</v>
+      </c>
+      <c r="L136" t="n">
+        <v>106</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.948</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:13.185</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1780022652269</v>
+      </c>
+      <c r="C137" t="n">
+        <v>83287</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-91.97</v>
+      </c>
+      <c r="E137" t="n">
+        <v>90</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1079</v>
+      </c>
+      <c r="G137" t="n">
+        <v>338.33</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J137" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K137" t="n">
+        <v>915</v>
+      </c>
+      <c r="L137" t="n">
+        <v>107</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:13.483</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1780022652469</v>
+      </c>
+      <c r="C138" t="n">
+        <v>83912</v>
+      </c>
+      <c r="D138" t="n">
+        <v>537.63</v>
+      </c>
+      <c r="E138" t="n">
+        <v>90</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1079</v>
+      </c>
+      <c r="G138" t="n">
+        <v>338.33</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J138" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K138" t="n">
+        <v>1014</v>
+      </c>
+      <c r="L138" t="n">
+        <v>119</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.821</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:13.533</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1780022652669</v>
+      </c>
+      <c r="C139" t="n">
+        <v>83208</v>
+      </c>
+      <c r="D139" t="n">
+        <v>-193.25</v>
+      </c>
+      <c r="E139" t="n">
+        <v>107</v>
+      </c>
+      <c r="F139" t="n">
+        <v>440</v>
+      </c>
+      <c r="G139" t="n">
+        <v>336.25</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J139" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K139" t="n">
+        <v>864</v>
+      </c>
+      <c r="L139" t="n">
+        <v>107</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.615</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:13.947</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1780022652869</v>
+      </c>
+      <c r="C140" t="n">
+        <v>83259</v>
+      </c>
+      <c r="D140" t="n">
+        <v>-132.59</v>
+      </c>
+      <c r="E140" t="n">
+        <v>107</v>
+      </c>
+      <c r="F140" t="n">
+        <v>440</v>
+      </c>
+      <c r="G140" t="n">
+        <v>336.25</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J140" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K140" t="n">
+        <v>1076</v>
+      </c>
+      <c r="L140" t="n">
+        <v>117</v>
+      </c>
+      <c r="M140" t="n">
+        <v>1.242</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:13.959</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1780022653069</v>
+      </c>
+      <c r="C141" t="n">
+        <v>83057</v>
+      </c>
+      <c r="D141" t="n">
+        <v>-327.96</v>
+      </c>
+      <c r="E141" t="n">
+        <v>107</v>
+      </c>
+      <c r="F141" t="n">
+        <v>440</v>
+      </c>
+      <c r="G141" t="n">
+        <v>336.25</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J141" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K141" t="n">
+        <v>888</v>
+      </c>
+      <c r="L141" t="n">
+        <v>106</v>
+      </c>
+      <c r="M141" t="n">
+        <v>1.383</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:14.345</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1780022653288</v>
+      </c>
+      <c r="C142" t="n">
+        <v>83205</v>
+      </c>
+      <c r="D142" t="n">
+        <v>-163.56</v>
+      </c>
+      <c r="E142" t="n">
+        <v>107</v>
+      </c>
+      <c r="F142" t="n">
+        <v>440</v>
+      </c>
+      <c r="G142" t="n">
+        <v>336.25</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J142" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1056</v>
+      </c>
+      <c r="L142" t="n">
+        <v>114</v>
+      </c>
+      <c r="M142" t="n">
+        <v>1.213</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:14.348</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1780022653488</v>
+      </c>
+      <c r="C143" t="n">
+        <v>83222</v>
+      </c>
+      <c r="D143" t="n">
+        <v>-138.39</v>
+      </c>
+      <c r="E143" t="n">
+        <v>107</v>
+      </c>
+      <c r="F143" t="n">
+        <v>440</v>
+      </c>
+      <c r="G143" t="n">
+        <v>336.25</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J143" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K143" t="n">
+        <v>858</v>
+      </c>
+      <c r="L143" t="n">
+        <v>108</v>
+      </c>
+      <c r="M143" t="n">
+        <v>1.831</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:14.830</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>1780022653688</v>
+      </c>
+      <c r="C144" t="n">
+        <v>82841</v>
+      </c>
+      <c r="D144" t="n">
+        <v>-512.47</v>
+      </c>
+      <c r="E144" t="n">
+        <v>92</v>
+      </c>
+      <c r="F144" t="n">
+        <v>919</v>
+      </c>
+      <c r="G144" t="n">
+        <v>323.72</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J144" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K144" t="n">
+        <v>1141</v>
+      </c>
+      <c r="L144" t="n">
+        <v>113</v>
+      </c>
+      <c r="M144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:14.838</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1780022653888</v>
+      </c>
+      <c r="C145" t="n">
+        <v>84332</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1004.16</v>
+      </c>
+      <c r="E145" t="n">
+        <v>92</v>
+      </c>
+      <c r="F145" t="n">
+        <v>919</v>
+      </c>
+      <c r="G145" t="n">
+        <v>323.72</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J145" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K145" t="n">
+        <v>949</v>
+      </c>
+      <c r="L145" t="n">
+        <v>106</v>
+      </c>
+      <c r="M145" t="n">
+        <v>1.263</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:15.165</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>1780022654088</v>
+      </c>
+      <c r="C146" t="n">
+        <v>82778</v>
+      </c>
+      <c r="D146" t="n">
+        <v>-600.05</v>
+      </c>
+      <c r="E146" t="n">
+        <v>101</v>
+      </c>
+      <c r="F146" t="n">
+        <v>400</v>
+      </c>
+      <c r="G146" t="n">
+        <v>252.4</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J146" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K146" t="n">
+        <v>1076</v>
+      </c>
+      <c r="L146" t="n">
+        <v>122</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:15.170</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>1780022654288</v>
+      </c>
+      <c r="C147" t="n">
+        <v>84302</v>
+      </c>
+      <c r="D147" t="n">
+        <v>953.95</v>
+      </c>
+      <c r="E147" t="n">
+        <v>101</v>
+      </c>
+      <c r="F147" t="n">
+        <v>400</v>
+      </c>
+      <c r="G147" t="n">
+        <v>252.4</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J147" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K147" t="n">
+        <v>882</v>
+      </c>
+      <c r="L147" t="n">
+        <v>124</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0.533</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:44:16.285</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>1780022654488</v>
+      </c>
+      <c r="C148" t="n">
+        <v>82647</v>
+      </c>
+      <c r="D148" t="n">
+        <v>-748.75</v>
+      </c>
+      <c r="E148" t="n">
+        <v>101</v>
+      </c>
+      <c r="F148" t="n">
+        <v>400</v>
+      </c>
+      <c r="G148" t="n">
+        <v>252.4</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J148" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K148" t="n">
+        <v>1795</v>
+      </c>
+      <c r="L148" t="n">
+        <v>130</v>
+      </c>
+      <c r="M148" t="n">
+        <v>1.651</v>
       </c>
     </row>
   </sheetData>
